--- a/output/pdf_financials_xlsx/SLF.xlsx
+++ b/output/pdf_financials_xlsx/SLF.xlsx
@@ -52622,7 +52622,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -65256,7 +65256,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E612" s="5" t="n">
